--- a/data/trans_orig/IP19-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19-Provincia-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40915</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51158</t>
+          <t>51075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77602</t>
+          <t>78246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>92414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61617</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>76487</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80054</t>
+          <t>80120</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>130616</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>151412</t>
+          <t>152745</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>25075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39945</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44198</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>57574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79703</t>
+          <t>79400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47517</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76493</t>
+          <t>76081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32523</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42938</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60740</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44508</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58327</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42134</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56170</t>
+          <t>56314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90332</t>
+          <t>91414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108978</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44994</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63640</t>
+          <t>62558</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43549</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>59213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>68,3%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26634</t>
+          <t>26387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>36306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46861</t>
+          <t>46853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38698</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48820</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77746</t>
+          <t>78390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19806</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>37397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>73890</t>
+          <t>71989</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91021</t>
+          <t>90709</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>86576</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104612</t>
+          <t>104078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>166457</t>
+          <t>166096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190589</t>
+          <t>190868</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>37913</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54732</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49173</t>
+          <t>49079</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73688</t>
+          <t>73409</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>97820</t>
+          <t>98181</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>102956</t>
+          <t>103462</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>121302</t>
+          <t>121646</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>119978</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>136125</t>
+          <t>136369</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>228521</t>
+          <t>227707</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>252649</t>
+          <t>252758</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36602</t>
+          <t>36258</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>54442</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45247</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>69313</t>
+          <t>69204</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>93441</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>489331</t>
+          <t>490910</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>529620</t>
+          <t>529383</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>938291</t>
+          <t>940082</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>997450</t>
+          <t>994693</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>193080</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>233369</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>405580</t>
+          <t>408337</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35153</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>46592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80797</t>
+          <t>80841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96852</t>
+          <t>96420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,67%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40226</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>62690</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77990</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66260</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>82904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135153</t>
+          <t>135824</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157525</t>
+          <t>157861</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>42023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58347</t>
+          <t>58011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80719</t>
+          <t>80048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>81443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100943</t>
+          <t>101382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30565</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>17506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59685</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>51651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>65726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101872</t>
+          <t>102566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122366</t>
+          <t>121605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31643</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34865</t>
+          <t>34946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42440</t>
+          <t>43042</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>32400</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>43932</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86482</t>
+          <t>87056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29748</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87193</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>105089</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88631</t>
+          <t>87467</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>106350</t>
+          <t>105977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>181567</t>
+          <t>180238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>207646</t>
+          <t>206510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32863</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51525</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38404</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>57287</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101905</t>
+          <t>103234</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>109992</t>
+          <t>110604</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>129074</t>
+          <t>129027</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>125080</t>
+          <t>126573</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>142477</t>
+          <t>143673</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>241162</t>
+          <t>242300</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>267315</t>
+          <t>268280</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>54716</t>
+          <t>54104</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>67021</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>94139</t>
+          <t>93001</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>512186</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>551823</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>996899</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1052203</t>
+          <t>1050824</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>237848</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39045</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90183</t>
+          <t>89464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>49200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64591</t>
+          <t>65875</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>80780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>68101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83995</t>
+          <t>83747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138658</t>
+          <t>138987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>160791</t>
+          <t>160666</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42237</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>53564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>75243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46132</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47845</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>59746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98711</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114696</t>
+          <t>114487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20699</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>38500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51978</t>
+          <t>52433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>42762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106068</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73875</t>
+          <t>73351</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>31193</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39558</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>31249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>66189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78302</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>44297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24714</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37833</t>
+          <t>37612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66737</t>
+          <t>67715</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84944</t>
+          <t>85975</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102648</t>
+          <t>103386</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119654</t>
+          <t>119890</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>193994</t>
+          <t>193668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>217486</t>
+          <t>217735</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>63960</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>87452</t>
+          <t>87778</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>118175</t>
+          <t>117249</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>134167</t>
+          <t>134066</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>121885</t>
+          <t>121762</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>139902</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>245543</t>
+          <t>245696</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>270429</t>
+          <t>270026</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>64596</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>28486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>46394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48884</t>
+          <t>48235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64209</t>
+          <t>63473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88581</t>
+          <t>88474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>43773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56506</t>
+          <t>56401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>41194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72329</t>
+          <t>70857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94488</t>
+          <t>97860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>43544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66712</t>
+          <t>66551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100808</t>
+          <t>100199</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165878</t>
+          <t>161411</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41528</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26430</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>45839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83506</t>
+          <t>84032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>40489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57122</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45103</t>
+          <t>45112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48706</t>
+          <t>47589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33018</t>
+          <t>33204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31869</t>
+          <t>32734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>24332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30029</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>52908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23313</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49036</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>82932</t>
+          <t>83144</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28468</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>36221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25834</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35434</t>
+          <t>35354</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51617</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>45255</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49749</t>
+          <t>50173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57395</t>
+          <t>58515</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87605</t>
+          <t>88050</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50276</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40383</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65265</t>
+          <t>64294</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>76009</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>108126</t>
+          <t>108781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>55728</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>52145</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77762</t>
+          <t>79136</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>95514</t>
+          <t>96381</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>127788</t>
+          <t>128139</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34176</t>
+          <t>33952</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>51368</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44485</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64380</t>
+          <t>64764</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>82565</t>
+          <t>83407</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>109537</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>54144</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75082</t>
+          <t>74709</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>61130</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>83362</t>
+          <t>83300</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>122811</t>
+          <t>121758</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>152262</t>
+          <t>152039</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>61885</t>
+          <t>62966</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>183798</t>
+          <t>183500</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>237122</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>208229</t>
+          <t>204326</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>259232</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>410612</t>
+          <t>409931</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>482949</t>
+          <t>482342</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>222501</t>
+          <t>224188</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>311047</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>256510</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>310574</t>
+          <t>309886</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>494285</t>
+          <t>496703</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>597464</t>
+          <t>596245</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
